--- a/data/trans_dic/IP2905_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2905_2023-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que durante sus primeros meses de vida solo recibieron lactancia materna</t>
+          <t>Menores que durante sus primeros meses de vida solo recibieron lactancia materna (tasa de respuesta: 98,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>46,41; 63,76</t>
+          <t>47,36; 63,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,46; 65,93</t>
+          <t>47,68; 65,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49,84; 62,42</t>
+          <t>49,6; 62,4</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,36; 57,57</t>
+          <t>40,2; 58,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,13; 57,16</t>
+          <t>39,61; 57,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,34; 55,06</t>
+          <t>42,78; 54,97</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,82; 60,63</t>
+          <t>37,76; 62,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,73; 62,38</t>
+          <t>40,07; 63,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42,34; 58,73</t>
+          <t>42,59; 58,37</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,06; 56,26</t>
+          <t>42,45; 56,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,44; 57,54</t>
+          <t>43,03; 57,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44,82; 55,01</t>
+          <t>44,43; 54,31</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>43,68; 60,14</t>
+          <t>42,81; 60,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,41; 64,13</t>
+          <t>44,6; 63,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,24; 59,85</t>
+          <t>46,58; 59,26</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31,95; 53,6</t>
+          <t>31,79; 53,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25,52; 47,69</t>
+          <t>26,47; 47,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32,06; 47,52</t>
+          <t>32,59; 46,93</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>46,58; 53,55</t>
+          <t>46,28; 53,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>46,6; 54,42</t>
+          <t>46,8; 54,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47,72; 52,84</t>
+          <t>47,42; 52,9</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que durante sus primeros meses de vida solo recibieron lactancia materna (tasa de respuesta: 98,87%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>55340</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>76012</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>131352</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>47426; 63718</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>63256; 86719</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>115474; 145273</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>45495</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>45230</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>90725</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>37545; 54869</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36930; 53269</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>79849; 102596</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>23583</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>32220</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>55803</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>18296; 30132</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>24975; 39274</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>47186; 64661</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>91071</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>105705</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>196776</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>78768; 104816</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>90743; 120495</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>176136; 215318</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>60071</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>84339</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>144410</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>49507; 69576</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>71124; 101634</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>128147; 163022</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>28912</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>24618</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>53530</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>21423; 35915</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>18019; 32436</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>44152; 63564</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>304473</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>368123</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>672595</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>282589; 328435</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>340051; 394512</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>634102; 707447</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2905_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2905_2023-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>47,36; 63,63</t>
+          <t>46,71; 63,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,68; 65,37</t>
+          <t>47,58; 65,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49,6; 62,4</t>
+          <t>50,65; 62,12</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,2; 58,75</t>
+          <t>39,53; 56,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,61; 57,13</t>
+          <t>39,16; 57,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,78; 54,97</t>
+          <t>42,36; 55,19</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,76; 62,19</t>
+          <t>36,87; 60,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,07; 63,01</t>
+          <t>39,37; 64,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42,59; 58,37</t>
+          <t>42,12; 59,38</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,45; 56,49</t>
+          <t>41,77; 56,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,03; 57,13</t>
+          <t>43,37; 57,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44,43; 54,31</t>
+          <t>44,8; 54,92</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>42,81; 60,17</t>
+          <t>43,61; 59,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>44,6; 63,74</t>
+          <t>44,29; 62,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,58; 59,26</t>
+          <t>46,0; 58,78</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31,79; 53,29</t>
+          <t>32,72; 53,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,47; 47,65</t>
+          <t>26,58; 47,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32,59; 46,93</t>
+          <t>31,47; 47,5</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>46,28; 53,79</t>
+          <t>46,31; 53,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>46,8; 54,29</t>
+          <t>46,94; 54,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47,42; 52,9</t>
+          <t>47,42; 52,77</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>47426; 63718</t>
+          <t>46780; 64069</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>63256; 86719</t>
+          <t>63123; 86262</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>115474; 145273</t>
+          <t>117919; 144618</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37545; 54869</t>
+          <t>36918; 53020</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36930; 53269</t>
+          <t>36511; 53366</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79849; 102596</t>
+          <t>79067; 102997</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18296; 30132</t>
+          <t>17865; 29460</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24975; 39274</t>
+          <t>24541; 40157</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47186; 64661</t>
+          <t>46659; 65784</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>78768; 104816</t>
+          <t>77505; 104813</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90743; 120495</t>
+          <t>91478; 120483</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>176136; 215318</t>
+          <t>177618; 217745</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>49507; 69576</t>
+          <t>50423; 68914</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>71124; 101634</t>
+          <t>70619; 100238</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>128147; 163022</t>
+          <t>126555; 161701</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>21423; 35915</t>
+          <t>22053; 36210</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18019; 32436</t>
+          <t>18093; 32295</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44152; 63564</t>
+          <t>42623; 64336</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>282589; 328435</t>
+          <t>282769; 326168</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>340051; 394512</t>
+          <t>341116; 398563</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>634102; 707447</t>
+          <t>634097; 705620</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2905_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2905_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,98%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>46,71; 63,98</t>
+          <t>49,97; 66,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,58; 65,02</t>
+          <t>46,08; 63,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50,65; 62,12</t>
+          <t>51,22; 62,67</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>49,06%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39,53; 56,77</t>
+          <t>39,72; 57,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,16; 57,23</t>
+          <t>40,56; 57,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,36; 55,19</t>
+          <t>42,81; 55,66</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>48,31%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,87; 60,81</t>
+          <t>38,51; 60,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,37; 64,42</t>
+          <t>35,75; 59,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42,12; 59,38</t>
+          <t>39,97; 56,75</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,1%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,77; 56,48</t>
+          <t>43,71; 57,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,37; 57,13</t>
+          <t>41,23; 53,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44,8; 54,92</t>
+          <t>44,53; 54,2</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,48%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>43,61; 59,6</t>
+          <t>43,13; 61,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>44,29; 62,86</t>
+          <t>45,98; 61,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,0; 58,78</t>
+          <t>46,28; 59,17</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>37,3%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32,72; 53,73</t>
+          <t>23,26; 44,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,58; 47,45</t>
+          <t>29,9; 52,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31,47; 47,5</t>
+          <t>30,25; 45,01</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>46,31; 53,42</t>
+          <t>46,48; 54,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>46,94; 54,85</t>
+          <t>46,25; 52,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47,42; 52,77</t>
+          <t>47,28; 52,29</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>82</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>55340</t>
+          <t>69809</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76012</t>
+          <t>54162</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>131352</t>
+          <t>123971</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>46780; 64069</t>
+          <t>59361; 79184</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>63123; 86262</t>
+          <t>45508; 62540</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>117919; 144618</t>
+          <t>111427; 136338</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>65</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>45495</t>
+          <t>43924</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>45230</t>
+          <t>46781</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90725</t>
+          <t>90706</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36918; 53020</t>
+          <t>35540; 51733</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36511; 53366</t>
+          <t>38703; 54797</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79067; 102997</t>
+          <t>79149; 102900</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23583</t>
+          <t>27798</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32220</t>
+          <t>23206</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55803</t>
+          <t>51004</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17865; 29460</t>
+          <t>21505; 33900</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24541; 40157</t>
+          <t>17779; 29622</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46659; 65784</t>
+          <t>42196; 59918</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>126</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>91071</t>
+          <t>98662</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>105705</t>
+          <t>81141</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>196776</t>
+          <t>179802</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>77505; 104813</t>
+          <t>85510; 113301</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>91478; 120483</t>
+          <t>70347; 91884</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>177618; 217745</t>
+          <t>163093; 198515</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>95</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>60071</t>
+          <t>74319</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>84339</t>
+          <t>62711</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>144410</t>
+          <t>137030</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>50423; 68914</t>
+          <t>62792; 89444</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>70619; 100238</t>
+          <t>53110; 71463</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>126555; 161701</t>
+          <t>120847; 154490</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>28912</t>
+          <t>21430</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>24618</t>
+          <t>28434</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53530</t>
+          <t>49864</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22053; 36210</t>
+          <t>15099; 28558</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18093; 32295</t>
+          <t>20558; 35976</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>42623; 64336</t>
+          <t>40438; 60172</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>444</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>463</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>304473</t>
+          <t>335943</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>368123</t>
+          <t>296435</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>672595</t>
+          <t>632379</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>282769; 326168</t>
+          <t>311500; 362701</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>341116; 398563</t>
+          <t>276968; 316223</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>634097; 705620</t>
+          <t>600035; 663607</t>
         </is>
       </c>
     </row>
